--- a/reports/pdf_change_20260731.xlsx
+++ b/reports/pdf_change_20260731.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 3,438억   ·   현금 150억(4.6%)      당일 2026-07-31  vs  전영업일 2026-07-30      매수 7종목  /  매도 5종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 3,286억   ·   현금 150억(4.6%)      당일 2026-07-31  vs  전영업일 2026-07-30      매수 7종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>31</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>921327750</v>
+        <v>925016750</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-27</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1316282400</v>
+        <v>-1321552800</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>31</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>636412950</v>
+        <v>638961150</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-14</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1251747000</v>
+        <v>-1256759000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>642856500</v>
+        <v>645430500</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-13</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-170259570</v>
+        <v>-170941290</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>629220150</v>
+        <v>631739550</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-11</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-202637160</v>
+        <v>-203448520</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>603495900</v>
+        <v>605912300</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-6</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-2235762000</v>
+        <v>-2244714000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>637362000</v>
+        <v>639914000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>5</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>791208000</v>
+        <v>794376000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,104억   ·   현금 13억(0.4%)      당일 2026-07-31  vs  전영업일 2026-07-30      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,004억   ·   현금 13억(0.4%)      당일 2026-07-31  vs  전영업일 2026-07-30      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -963,7 +963,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 1,929억   ·   현금 33억(1.8%)      당일 2026-07-31  vs  전영업일 2026-07-30      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 1,812억   ·   현금 32억(1.8%)      당일 2026-07-31  vs  전영업일 2026-07-30      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -987,7 +987,7 @@
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,829억   ·   현금 33억(1.9%)      당일 2026-07-31  vs  전영업일 2026-07-30      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,799억   ·   현금 34억(1.9%)      당일 2026-07-31  vs  전영업일 2026-07-30      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -1011,7 +1011,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 218억   ·   현금 7억(3.2%)      당일 2026-07-31  vs  전영업일 2026-07-30      매수 5종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 212억   ·   현금 7억(3.4%)      당일 2026-07-31  vs  전영업일 2026-07-30      매수 5종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1107,11 +1107,11 @@
         <v>33</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>74111400</v>
+        <v>69973200</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>7.09%→7.43%</t>
+          <t>7.01%→7.36%</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
@@ -1128,11 +1128,11 @@
         <v>-145</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-35098700</v>
+        <v>-35319100</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>2.98%→2.81%</t>
+          <t>3.13%→2.96%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
@@ -1151,11 +1151,11 @@
         <v>28</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>50008000</v>
+        <v>47241600</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>2.35%→2.58%</t>
+          <t>2.32%→2.56%</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -1172,11 +1172,11 @@
         <v>-91</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-43778280</v>
+        <v>-44884840</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>1.06%→0.85%</t>
+          <t>1.14%→0.92%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
@@ -1195,11 +1195,11 @@
         <v>15</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>65094000</v>
+        <v>57684000</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>3.45%→3.76%</t>
+          <t>3.20%→3.49%</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -1216,11 +1216,11 @@
         <v>-6</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-107388000</v>
+        <v>-103512000</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>2.03%→1.52%</t>
+          <t>2.05%→1.54%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
@@ -1239,11 +1239,11 @@
         <v>11</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>46732400</v>
+        <v>43304800</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>1.71%→1.93%</t>
+          <t>1.66%→1.87%</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -1260,11 +1260,11 @@
         <v>-3</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-64410000</v>
+        <v>-63726000</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>1.73%→1.42%</t>
+          <t>1.79%→1.47%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -1283,11 +1283,11 @@
         <v>4</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>34929600</v>
+        <v>30825600</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>2.98%→3.14%</t>
+          <t>2.75%→2.90%</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -1304,7 +1304,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 433억   ·   현금 12억(2.9%)      당일 2026-07-31  vs  전영업일 2026-07-30      매수 0종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 418억   ·   현금 12억(2.9%)      당일 2026-07-31  vs  전영업일 2026-07-30      매수 0종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1405,7 +1405,7 @@
         <v>-5</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-104500000</v>
+        <v>-106400000</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>-4</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-122980000</v>
+        <v>-125216000</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>

--- a/reports/pdf_change_20260731.xlsx
+++ b/reports/pdf_change_20260731.xlsx
@@ -663,23 +663,23 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지  (신규)</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B6" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>925016750</v>
+        <v>638961150</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.30%</t>
+          <t>3.03%→3.29%</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>0→31</t>
+          <t>464→495</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -707,23 +707,23 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>지엔씨에너지  (신규)</t>
         </is>
       </c>
       <c r="B7" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>638961150</v>
+        <v>925016750</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>3.03%→3.29%</t>
+          <t>0.00%→0.30%</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>464→495</t>
+          <t>0→31</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
